--- a/11_Demos_and_Workbooks/02_Data_Management/Module_2_Test.xlsx
+++ b/11_Demos_and_Workbooks/02_Data_Management/Module_2_Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\02_Data_Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43EC57A1-0F60-4ABB-AE52-67D79014FDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C165A6-5511-4E96-A468-3795A944AD95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="725" activeTab="1" xr2:uid="{B30C8FC3-31A0-430B-B35F-9B92D7954CD8}"/>
   </bookViews>
@@ -1407,7 +1407,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C17">
-    <cfRule type="dataBar" priority="2">
+    <cfRule type="dataBar" priority="3">
       <dataBar showValue="0">
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1421,7 +1421,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E17">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1430,6 +1430,15 @@
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G17">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="3Flags">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="35"/>
+        <cfvo type="percent" val="70"/>
+      </iconSet>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
